--- a/product-definitions/spreadsheet/mean-winds.xlsx
+++ b/product-definitions/spreadsheet/mean-winds.xlsx
@@ -263,7 +263,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -289,7 +289,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -297,10 +296,6 @@
     </font>
     <font>
       <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -319,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -334,15 +329,11 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -351,20 +342,17 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1669,7 +1657,7 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1709,7 +1697,7 @@
       <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1717,7 +1705,7 @@
       <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1725,7 +1713,7 @@
       <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1755,7 +1743,7 @@
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1787,7 +1775,7 @@
       <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1795,7 +1783,7 @@
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1803,7 +1791,7 @@
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1811,7 +1799,7 @@
       <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1819,7 +1807,7 @@
       <c r="B23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1841,7 +1829,7 @@
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1873,7 +1861,7 @@
       <c r="B31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1881,7 +1869,7 @@
       <c r="B32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1889,7 +1877,7 @@
       <c r="B33" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1897,7 +1885,7 @@
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1919,7 +1907,7 @@
     </row>
     <row r="37" ht="12.0" customHeight="1"/>
     <row r="38" ht="12.0" customHeight="1">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1927,7 +1915,7 @@
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1951,7 +1939,7 @@
       <c r="B42" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1959,7 +1947,7 @@
       <c r="B43" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1967,7 +1955,7 @@
       <c r="B44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1975,7 +1963,7 @@
       <c r="B45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1983,7 +1971,7 @@
       <c r="B46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1991,7 +1979,7 @@
       <c r="B47" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2013,7 +2001,7 @@
       <c r="B51" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2045,7 +2033,7 @@
       <c r="B55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2053,7 +2041,7 @@
       <c r="B56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2061,7 +2049,7 @@
       <c r="B57" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2069,7 +2057,7 @@
       <c r="B58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2099,7 +2087,7 @@
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2131,7 +2119,7 @@
       <c r="B67" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2139,7 +2127,7 @@
       <c r="B68" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2147,7 +2135,7 @@
       <c r="B69" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2155,7 +2143,7 @@
       <c r="B70" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2185,7 +2173,7 @@
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2217,7 +2205,7 @@
       <c r="B79" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2225,7 +2213,7 @@
       <c r="B80" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2233,7 +2221,7 @@
       <c r="B81" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2241,7 +2229,7 @@
       <c r="B82" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2263,7 +2251,7 @@
     </row>
     <row r="85" ht="12.0" customHeight="1"/>
     <row r="86" ht="12.0" customHeight="1">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2271,7 +2259,7 @@
       <c r="B87" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2295,7 +2283,7 @@
       <c r="B90" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2303,7 +2291,7 @@
       <c r="B91" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2311,7 +2299,7 @@
       <c r="B92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2319,7 +2307,7 @@
       <c r="B93" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2327,7 +2315,7 @@
       <c r="B94" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2349,7 +2337,7 @@
     </row>
     <row r="97" ht="12.0" customHeight="1"/>
     <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2357,7 +2345,7 @@
       <c r="B99" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2373,7 +2361,7 @@
       <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2381,8 +2369,8 @@
       <c r="B102" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="10"/>
-      <c r="D102" s="6" t="s">
+      <c r="C102" s="8"/>
+      <c r="D102" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2390,7 +2378,7 @@
       <c r="B103" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="9" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2398,7 +2386,7 @@
       <c r="B104" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2406,7 +2394,7 @@
       <c r="B105" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2414,7 +2402,7 @@
       <c r="B106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2445,7 +2433,7 @@
       <c r="B112" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2477,7 +2465,7 @@
       <c r="B116" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2485,7 +2473,7 @@
       <c r="B117" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2493,7 +2481,7 @@
       <c r="B118" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2501,7 +2489,7 @@
       <c r="B119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2531,7 +2519,7 @@
       <c r="B124" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2563,7 +2551,7 @@
       <c r="B128" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2571,7 +2559,7 @@
       <c r="B129" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2579,7 +2567,7 @@
       <c r="B130" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2587,7 +2575,7 @@
       <c r="B131" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2617,7 +2605,7 @@
       <c r="B136" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2641,7 +2629,7 @@
       <c r="B139" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C139" s="11"/>
+      <c r="C139" s="9"/>
       <c r="D139" s="5" t="s">
         <v>49</v>
       </c>
@@ -2650,7 +2638,7 @@
       <c r="B140" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C140" s="11" t="s">
+      <c r="C140" s="9" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2658,7 +2646,7 @@
       <c r="B141" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2666,7 +2654,7 @@
       <c r="B142" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2674,7 +2662,7 @@
       <c r="B143" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2704,7 +2692,7 @@
       <c r="B148" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2736,7 +2724,7 @@
       <c r="B152" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C152" s="6" t="s">
+      <c r="C152" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2744,7 +2732,7 @@
       <c r="B153" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C153" s="7">
+      <c r="C153" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2752,7 +2740,7 @@
       <c r="B154" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2760,7 +2748,7 @@
       <c r="B155" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2782,7 +2770,7 @@
     </row>
     <row r="158" ht="12.0" customHeight="1"/>
     <row r="159" ht="12.0" customHeight="1">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2790,7 +2778,7 @@
       <c r="B160" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C160" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2814,7 +2802,7 @@
       <c r="B163" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D163" s="6" t="s">
+      <c r="D163" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2822,7 +2810,7 @@
       <c r="B164" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C164" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2830,7 +2818,7 @@
       <c r="B165" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C165" s="7">
+      <c r="C165" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2838,7 +2826,7 @@
       <c r="B166" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2846,7 +2834,7 @@
       <c r="B167" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2868,7 +2856,7 @@
     </row>
     <row r="170" ht="12.0" customHeight="1"/>
     <row r="171" ht="12.0" customHeight="1">
-      <c r="A171" s="6" t="s">
+      <c r="A171" s="5" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2876,7 +2864,7 @@
       <c r="B172" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C172" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2892,7 +2880,7 @@
       <c r="B174" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C174" s="12">
+      <c r="C174" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -2900,7 +2888,7 @@
       <c r="B175" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C175" s="12"/>
+      <c r="C175" s="10"/>
     </row>
     <row r="176" ht="12.0" customHeight="1">
       <c r="B176" s="5" t="s">
@@ -2911,28 +2899,28 @@
       </c>
     </row>
     <row r="177" ht="12.0" customHeight="1">
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C177" s="14" t="s">
+      <c r="C177" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
-      <c r="F177" s="13"/>
-      <c r="G177" s="13"/>
-    </row>
-    <row r="178">
-      <c r="B178" s="15" t="s">
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="11"/>
+      <c r="G177" s="11"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="B178" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C178" s="16" t="s">
+      <c r="C178" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D178" s="13"/>
-      <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
-      <c r="G178" s="13"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
     </row>
     <row r="179" ht="12.0" customHeight="1"/>
     <row r="180" ht="12.0" customHeight="1">
@@ -2944,7 +2932,7 @@
       <c r="B181" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C181" s="6" t="s">
+      <c r="C181" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2960,7 +2948,7 @@
       <c r="B183" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C183" s="12">
+      <c r="C183" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -2968,7 +2956,7 @@
       <c r="B184" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C184" s="12"/>
+      <c r="C184" s="10"/>
     </row>
     <row r="185" ht="12.0" customHeight="1">
       <c r="B185" s="5" t="s">
@@ -2979,18 +2967,18 @@
       </c>
     </row>
     <row r="186" ht="12.0" customHeight="1">
-      <c r="B186" s="13" t="s">
+      <c r="B186" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C186" s="14" t="s">
+      <c r="C186" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="187">
-      <c r="B187" s="15" t="s">
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="B187" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C187" s="17" t="s">
+      <c r="C187" s="14" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3004,7 +2992,7 @@
       <c r="B190" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C190" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3020,7 +3008,7 @@
       <c r="B192" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C192" s="12">
+      <c r="C192" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -3028,7 +3016,7 @@
       <c r="B193" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C193" s="12"/>
+      <c r="C193" s="10"/>
     </row>
     <row r="194" ht="12.0" customHeight="1">
       <c r="B194" s="5" t="s">
@@ -3039,18 +3027,18 @@
       </c>
     </row>
     <row r="195" ht="12.0" customHeight="1">
-      <c r="B195" s="13" t="s">
+      <c r="B195" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C195" s="14" t="s">
+      <c r="C195" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="196">
-      <c r="B196" s="15" t="s">
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="B196" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C196" s="17" t="s">
+      <c r="C196" s="14" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3064,7 +3052,7 @@
       <c r="B199" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="6" t="s">
+      <c r="C199" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3080,7 +3068,7 @@
       <c r="B201" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C201" s="12">
+      <c r="C201" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -3088,29 +3076,29 @@
       <c r="B202" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C202" s="12"/>
+      <c r="C202" s="10"/>
     </row>
     <row r="203" ht="12.0" customHeight="1">
       <c r="B203" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C203" s="6" t="s">
+      <c r="C203" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="204" ht="12.0" customHeight="1">
-      <c r="B204" s="13" t="s">
+      <c r="B204" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C204" s="14" t="s">
+      <c r="C204" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="205">
-      <c r="B205" s="15" t="s">
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="B205" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C205" s="16" t="s">
+      <c r="C205" s="14" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3124,7 +3112,7 @@
       <c r="B208" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C208" s="6" t="s">
+      <c r="C208" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3140,7 +3128,7 @@
       <c r="B210" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C210" s="12">
+      <c r="C210" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -3148,35 +3136,35 @@
       <c r="B211" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C211" s="12"/>
+      <c r="C211" s="10"/>
     </row>
     <row r="212" ht="12.0" customHeight="1">
       <c r="B212" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C212" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="213" ht="12.0" customHeight="1">
-      <c r="B213" s="13" t="s">
+      <c r="B213" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C213" s="14" t="s">
+      <c r="C213" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="214">
-      <c r="B214" s="15" t="s">
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="B214" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C214" s="16" t="s">
+      <c r="C214" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="215" ht="12.0" customHeight="1"/>
     <row r="216" ht="12.0" customHeight="1">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3184,7 +3172,7 @@
       <c r="B217" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3200,7 +3188,7 @@
       <c r="B219" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C219" s="12">
+      <c r="C219" s="10">
         <v>1.0</v>
       </c>
     </row>
@@ -3208,29 +3196,29 @@
       <c r="B220" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C220" s="12"/>
+      <c r="C220" s="10"/>
     </row>
     <row r="221" ht="12.0" customHeight="1">
       <c r="B221" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="C221" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="222" ht="12.0" customHeight="1">
-      <c r="B222" s="13" t="s">
+      <c r="B222" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C222" s="14" t="s">
+      <c r="C222" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="223">
-      <c r="B223" s="15" t="s">
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="B223" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C223" s="16" t="s">
+      <c r="C223" s="14" t="s">
         <v>72</v>
       </c>
     </row>
